--- a/data/trans_orig/IP05B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05B-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>33631</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47211</t>
+          <t>47924</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68178</t>
+          <t>69019</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56846</t>
+          <t>56240</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72595</t>
+          <t>72314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62679</t>
+          <t>62009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79716</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125185</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148419</t>
+          <t>148074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>20843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36622</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43714</t>
+          <t>43872</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>64352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>45803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66181</t>
+          <t>67553</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95369</t>
+          <t>94270</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>124836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149347</t>
+          <t>150909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174598</t>
+          <t>175479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151693</t>
+          <t>150720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175579</t>
+          <t>176480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>307816</t>
+          <t>309063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343365</t>
+          <t>343702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>39771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60511</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>37265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38302</t>
+          <t>37659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47451</t>
+          <t>48244</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>70816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63392</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>80477</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>79535</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97898</t>
+          <t>97505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148989</t>
+          <t>149003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174866</t>
+          <t>172988</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51431</t>
+          <t>50521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>28832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46202</t>
+          <t>45892</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>88209</t>
+          <t>87967</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>121394</t>
+          <t>120283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142023</t>
+          <t>141719</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126480</t>
+          <t>127882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148840</t>
+          <t>149035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>254965</t>
+          <t>254441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>284217</t>
+          <t>286067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24751</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>29068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47636</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
+          <t>129566</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163121</t>
+          <t>164779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140224</t>
+          <t>139914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174449</t>
+          <t>175532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>279920</t>
+          <t>278649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>331962</t>
+          <t>329088</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>411640</t>
+          <t>410425</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>452777</t>
+          <t>452197</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>441836</t>
+          <t>443374</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>482870</t>
+          <t>482392</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>864439</t>
+          <t>867001</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>922481</t>
+          <t>921253</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>63982</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90374</t>
+          <t>90932</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66437</t>
+          <t>67079</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>93231</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136102</t>
+          <t>138522</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>175642</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52711</t>
+          <t>53122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98022</t>
+          <t>98244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115560</t>
+          <t>115705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98680</t>
+          <t>98449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115933</t>
+          <t>115871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202182</t>
+          <t>201644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226789</t>
+          <t>225945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39202</t>
+          <t>39499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>44212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44408</t>
+          <t>44394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57504</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83530</t>
+          <t>82924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158656</t>
+          <t>159182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181522</t>
+          <t>181664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180025</t>
+          <t>180785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204646</t>
+          <t>205068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347612</t>
+          <t>345585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>380885</t>
+          <t>380306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>34136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>45383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47727</t>
+          <t>47796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72595</t>
+          <t>73305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>34207</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55127</t>
+          <t>54899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105165</t>
+          <t>104693</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123857</t>
+          <t>122913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111285</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129314</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>222279</t>
+          <t>222629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>247065</t>
+          <t>246909</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>40826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -6421,82 +6421,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5729</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19142</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>34606</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>63342</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110522</t>
+          <t>110082</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129777</t>
+          <t>129624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116424</t>
+          <t>114013</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135791</t>
+          <t>134990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>232165</t>
+          <t>232854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>260657</t>
+          <t>260139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28090</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56824</t>
+          <t>56893</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,42 +7158,42 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>11311</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2394</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>10572</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,47 +7266,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>20429</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>13970</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>29862</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>20429</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>13676</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>29674</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90886</t>
+          <t>91233</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>122458</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86061</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116284</t>
+          <t>117067</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>186518</t>
+          <t>184441</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230468</t>
+          <t>227281</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>493658</t>
+          <t>494033</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>531448</t>
+          <t>533298</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>527141</t>
+          <t>527775</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>566935</t>
+          <t>566293</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1029434</t>
+          <t>1032057</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1086650</t>
+          <t>1089373</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93435</t>
+          <t>91657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>76181</t>
+          <t>76216</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>105152</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>148268</t>
+          <t>147835</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>189728</t>
+          <t>189162</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21516</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41485</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89240</t>
+          <t>89368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66091</t>
+          <t>66041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83567</t>
+          <t>84431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142906</t>
+          <t>141684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167718</t>
+          <t>167325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42236</t>
+          <t>41240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>52876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75630</t>
+          <t>74704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>35031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37391</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>45412</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67272</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113714</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135906</t>
+          <t>135827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156973</t>
+          <t>157466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182668</t>
+          <t>182644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280205</t>
+          <t>277991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313022</t>
+          <t>311733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>42247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62366</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44918</t>
+          <t>44757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66742</t>
+          <t>66568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93521</t>
+          <t>94882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122211</t>
+          <t>123684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35137</t>
+          <t>35204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99140</t>
+          <t>98073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121118</t>
+          <t>119979</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100948</t>
+          <t>101043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123934</t>
+          <t>123717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>204083</t>
+          <t>205225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237165</t>
+          <t>237758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,09%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61374</t>
+          <t>62233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60090</t>
+          <t>60858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86792</t>
+          <t>89765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117900</t>
+          <t>117569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33494</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>54992</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>100926</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123848</t>
+          <t>122636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97786</t>
+          <t>97594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119756</t>
+          <t>119214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208337</t>
+          <t>206616</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237648</t>
+          <t>236816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27540</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44842</t>
+          <t>44552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>50471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63658</t>
+          <t>63501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89434</t>
+          <t>88374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,47 +10795,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>6474</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>11355</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103261</t>
+          <t>104643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>154914</t>
+          <t>155146</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196224</t>
+          <t>196394</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>407538</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>449317</t>
+          <t>448179</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>444786</t>
+          <t>444823</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>487632</t>
+          <t>486019</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>866538</t>
+          <t>862887</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>923895</t>
+          <t>925337</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153802</t>
+          <t>151254</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>189987</t>
+          <t>189226</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>160275</t>
+          <t>161254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>196552</t>
+          <t>198323</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>322510</t>
+          <t>321932</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>375675</t>
+          <t>374741</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37553</t>
+          <t>37358</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47982</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74715</t>
+          <t>74118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89053</t>
+          <t>89759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>32346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104932</t>
+          <t>103904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123576</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117049</t>
+          <t>116198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138552</t>
+          <t>138545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227677</t>
+          <t>230141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255901</t>
+          <t>257255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26566</t>
+          <t>26431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44616</t>
+          <t>44723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56543</t>
+          <t>56097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82106</t>
+          <t>80694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38329</t>
+          <t>39113</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>111954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133918</t>
+          <t>134032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150168</t>
+          <t>151674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175236</t>
+          <t>175790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272005</t>
+          <t>271611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>303328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42843</t>
+          <t>44125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47254</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53585</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84242</t>
+          <t>84025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99551</t>
+          <t>99907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127422</t>
+          <t>120811</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127371</t>
+          <t>120458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206639</t>
+          <t>205961</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>219200</t>
+          <t>221448</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>253400</t>
+          <t>253646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>351867</t>
+          <t>350571</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>447435</t>
+          <t>450035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58174</t>
+          <t>56861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>69102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76975</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>115606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>151151</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65769</t>
+          <t>63997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>77524</t>
+          <t>75235</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109196</t>
+          <t>108821</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>398278</t>
+          <t>401067</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>484861</t>
+          <t>486425</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>551129</t>
+          <t>551811</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>596911</t>
+          <t>598862</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>970085</t>
+          <t>963060</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1067562</t>
+          <t>1069687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>103757</t>
+          <t>103565</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>142706</t>
+          <t>141688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>115272</t>
+          <t>116583</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>158708</t>
+          <t>159472</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230447</t>
+          <t>231868</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>286843</t>
+          <t>290849</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
